--- a/data/trans_bre/P20-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P20-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,03</t>
+          <t>-1,08; 2,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,32</t>
+          <t>-2,93; 2,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,64</t>
+          <t>-1,88; 3,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,15; -0,78</t>
+          <t>-6,6; -0,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 55,84</t>
+          <t>-15,18; 51,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 26,39</t>
+          <t>-24,42; 27,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 61,63</t>
+          <t>-21,5; 58,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-50,06; -8,58</t>
+          <t>-49,47; -9,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,07</t>
+          <t>2,97; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,11</t>
+          <t>2,82; 6,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,82</t>
+          <t>1,8; 4,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,98</t>
+          <t>-0,75; 2,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,84; 292,57</t>
+          <t>87,56; 281,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,47; 144,32</t>
+          <t>49,93; 147,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,5; 138,24</t>
+          <t>37,16; 137,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 90,11</t>
+          <t>-14,19; 88,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,04</t>
+          <t>0,31; 6,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 10,1</t>
+          <t>3,65; 9,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,98</t>
+          <t>0,77; 6,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,47</t>
+          <t>-1,6; 3,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 200,16</t>
+          <t>0,48; 213,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,61; 575,53</t>
+          <t>74,44; 570,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 212,74</t>
+          <t>8,6; 212,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 79,38</t>
+          <t>-22,63; 83,19</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,51</t>
+          <t>2,26; 4,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,8</t>
+          <t>2,07; 4,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,07</t>
+          <t>1,75; 4,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,87</t>
+          <t>-0,91; 2,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,27; 120,95</t>
+          <t>45,69; 120,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,84; 86,71</t>
+          <t>31,15; 87,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,14; 94,27</t>
+          <t>31,7; 94,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 41,03</t>
+          <t>-14,94; 44,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P20-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,37</t>
+          <t>-2,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-31,19%</t>
+          <t>-26,82%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,92</t>
+          <t>-0,97; 3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,28</t>
+          <t>-2,87; 2,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,44</t>
+          <t>-1,45; 3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; -0,84</t>
+          <t>-5,32; -0,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 51,91</t>
+          <t>-13,07; 57,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 27,25</t>
+          <t>-24,31; 26,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 58,02</t>
+          <t>-17,46; 58,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,47; -9,38</t>
+          <t>-45,31; -2,77</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,95</t>
+          <t>2,96; 6,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,28</t>
+          <t>2,48; 6,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,59</t>
+          <t>1,96; 4,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,83</t>
+          <t>-0,04; 2,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,56; 281,07</t>
+          <t>89,86; 294,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,93; 147,58</t>
+          <t>44,86; 154,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,16; 137,83</t>
+          <t>41,37; 142,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 88,38</t>
+          <t>-1,08; 68,66</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,41</t>
+          <t>0,11; 6,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,94</t>
+          <t>3,45; 10,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,97</t>
+          <t>0,47; 6,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,64</t>
+          <t>-1,61; 3,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 213,03</t>
+          <t>-1,29; 194,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,44; 570,43</t>
+          <t>65,29; 551,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 212,02</t>
+          <t>6,32; 192,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 83,19</t>
+          <t>-21,97; 77,92</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,46</t>
+          <t>2,04; 4,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,76</t>
+          <t>2,17; 4,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,08</t>
+          <t>1,62; 4,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,02</t>
+          <t>-0,36; 1,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,69; 120,31</t>
+          <t>44,22; 120,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,15; 87,42</t>
+          <t>32,23; 87,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,7; 94,03</t>
+          <t>29,52; 94,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 44,66</t>
+          <t>-5,6; 33,92</t>
         </is>
       </c>
     </row>
